--- a/区域映射表.xlsx
+++ b/区域映射表.xlsx
@@ -1,53 +1,798 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\龙二\进出口\6910进出口统计\02_标准模板\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13DC037-C84E-4BDE-944B-A2681DF0CEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="840" yWindow="405" windowWidth="14415" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="区域映射" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">区域映射!$A$1:$C$230</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="246">
   <si>
     <t>原始名称</t>
   </si>
   <si>
+    <t>标准名称</t>
+  </si>
+  <si>
+    <t>不丹</t>
+  </si>
+  <si>
+    <t>东帝汶</t>
+  </si>
+  <si>
+    <t>中国台湾</t>
+  </si>
+  <si>
+    <t>中国澳门</t>
+  </si>
+  <si>
+    <t>中国香港</t>
+  </si>
+  <si>
+    <t>中非</t>
+  </si>
+  <si>
+    <t>丹麦</t>
+  </si>
+  <si>
+    <t>乌克兰</t>
+  </si>
+  <si>
+    <t>乌兹别克斯坦</t>
+  </si>
+  <si>
+    <t>乌干达</t>
+  </si>
+  <si>
+    <t>乌拉圭</t>
+  </si>
+  <si>
+    <t>乍得</t>
+  </si>
+  <si>
+    <t>也门</t>
+  </si>
+  <si>
+    <t>亚美尼亚</t>
+  </si>
+  <si>
+    <t>以色列</t>
+  </si>
+  <si>
+    <t>伊拉克</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>伯利兹</t>
+  </si>
+  <si>
+    <t>佛得角</t>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+  </si>
+  <si>
+    <t>保加利亚</t>
+  </si>
+  <si>
+    <t>克罗地亚</t>
+  </si>
+  <si>
+    <t>关岛</t>
+  </si>
+  <si>
+    <t>冈比亚</t>
+  </si>
+  <si>
+    <t>冰岛</t>
+  </si>
+  <si>
+    <t>几内亚</t>
+  </si>
+  <si>
+    <t>几内亚比绍</t>
+  </si>
+  <si>
+    <t>刚果共和国</t>
+  </si>
+  <si>
+    <t>刚果民主共和国</t>
+  </si>
+  <si>
+    <t>利比亚</t>
+  </si>
+  <si>
+    <t>利比里亚</t>
+  </si>
+  <si>
+    <t>加拿大</t>
+  </si>
+  <si>
+    <t>加纳</t>
+  </si>
+  <si>
+    <t>加蓬</t>
+  </si>
+  <si>
+    <t>加那利群岛</t>
+  </si>
+  <si>
+    <t>匈牙利</t>
+  </si>
+  <si>
+    <t>北马其顿</t>
+  </si>
+  <si>
+    <t>北马里亚纳群岛</t>
+  </si>
+  <si>
+    <t>南苏丹</t>
+  </si>
+  <si>
+    <t>南非</t>
+  </si>
+  <si>
+    <t>博内尔</t>
+  </si>
+  <si>
+    <t>博纳尔，圣俄斯塔休斯和萨巴</t>
+  </si>
+  <si>
+    <t>博茨瓦纳</t>
+  </si>
+  <si>
+    <t>卡塔尔</t>
+  </si>
+  <si>
+    <t>卢旺达</t>
+  </si>
+  <si>
+    <t>卢森堡</t>
+  </si>
+  <si>
+    <t>印度</t>
+  </si>
+  <si>
+    <t>印度尼西亚</t>
+  </si>
+  <si>
+    <t>危地马拉</t>
+  </si>
+  <si>
+    <t>厄瓜多尔</t>
+  </si>
+  <si>
+    <t>厄立特里亚</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>古巴</t>
+  </si>
+  <si>
+    <t>吉尔吉斯斯坦</t>
+  </si>
+  <si>
+    <t>吉布提</t>
+  </si>
+  <si>
+    <t>哈萨克斯坦</t>
+  </si>
+  <si>
+    <t>哥伦比亚</t>
+  </si>
+  <si>
+    <t>哥斯达黎加</t>
+  </si>
+  <si>
+    <t>喀麦隆</t>
+  </si>
+  <si>
+    <t>图瓦卢</t>
+  </si>
+  <si>
+    <t>土库曼斯坦</t>
+  </si>
+  <si>
+    <t>土耳其</t>
+  </si>
+  <si>
+    <t>圣卢西亚</t>
+  </si>
+  <si>
+    <t>圣基茨和尼维斯</t>
+  </si>
+  <si>
+    <t>圣多美和普林西比</t>
+  </si>
+  <si>
+    <t>圣巴泰勒米</t>
+  </si>
+  <si>
+    <t>圣文森特和格林纳丁斯</t>
+  </si>
+  <si>
+    <t>圭亚那</t>
+  </si>
+  <si>
+    <t>坦桑尼亚</t>
+  </si>
+  <si>
+    <t>埃及</t>
+  </si>
+  <si>
+    <t>埃塞俄比亚</t>
+  </si>
+  <si>
+    <t>基里巴斯</t>
+  </si>
+  <si>
+    <t>塔吉克斯坦</t>
+  </si>
+  <si>
+    <t>塞内加尔</t>
+  </si>
+  <si>
+    <t>塞尔维亚</t>
+  </si>
+  <si>
+    <t>塞拉利昂</t>
+  </si>
+  <si>
+    <t>塞浦路斯</t>
+  </si>
+  <si>
+    <t>塞舌尔</t>
+  </si>
+  <si>
+    <t>墨西哥</t>
+  </si>
+  <si>
+    <t>多哥</t>
+  </si>
+  <si>
+    <t>多米尼克</t>
+  </si>
+  <si>
+    <t>多米尼加</t>
+  </si>
+  <si>
+    <t>大洋洲其他国家(地区)</t>
+  </si>
+  <si>
+    <t>奥地利</t>
+  </si>
+  <si>
+    <t>委内瑞拉</t>
+  </si>
+  <si>
+    <t>孟加拉国</t>
+  </si>
+  <si>
+    <t>安哥拉</t>
+  </si>
+  <si>
+    <t>安圭拉</t>
+  </si>
+  <si>
+    <t>安提瓜和巴布达</t>
+  </si>
+  <si>
+    <t>安道尔</t>
+  </si>
+  <si>
+    <t>密克罗尼西亚联邦</t>
+  </si>
+  <si>
+    <t>尼加拉瓜</t>
+  </si>
+  <si>
+    <t>尼日利亚</t>
+  </si>
+  <si>
+    <t>尼日尔</t>
+  </si>
+  <si>
+    <t>尼泊尔</t>
+  </si>
+  <si>
+    <t>巴勒斯坦</t>
+  </si>
+  <si>
+    <t>巴哈马</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>巴巴多斯</t>
+  </si>
+  <si>
+    <t>巴布亚新几内亚</t>
+  </si>
+  <si>
+    <t>巴拉圭</t>
+  </si>
+  <si>
+    <t>巴拿马</t>
+  </si>
+  <si>
+    <t>巴林</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>布基纳法索</t>
+  </si>
+  <si>
+    <t>布维岛</t>
+  </si>
+  <si>
+    <t>布隆迪</t>
+  </si>
+  <si>
+    <t>希腊</t>
+  </si>
+  <si>
+    <t>帕劳</t>
+  </si>
+  <si>
+    <t>库克群岛</t>
+  </si>
+  <si>
+    <t>库拉索</t>
+  </si>
+  <si>
+    <t>开曼群岛</t>
+  </si>
+  <si>
+    <t>德国</t>
+  </si>
+  <si>
+    <t>意大利</t>
+  </si>
+  <si>
+    <t>所罗门群岛</t>
+  </si>
+  <si>
+    <t>拉丁美洲其他国家(地区)</t>
+  </si>
+  <si>
+    <t>拉脱维亚</t>
+  </si>
+  <si>
+    <t>挪威</t>
+  </si>
+  <si>
+    <t>捷克</t>
+  </si>
+  <si>
+    <t>摩尔多瓦</t>
+  </si>
+  <si>
+    <t>摩洛哥</t>
+  </si>
+  <si>
+    <t>摩纳哥</t>
+  </si>
+  <si>
+    <t>文莱</t>
+  </si>
+  <si>
+    <t>斐济</t>
+  </si>
+  <si>
+    <t>斯威士兰</t>
+  </si>
+  <si>
+    <t>斯洛伐克</t>
+  </si>
+  <si>
+    <t>斯洛文尼亚</t>
+  </si>
+  <si>
+    <t>斯里兰卡</t>
+  </si>
+  <si>
+    <t>新加坡</t>
+  </si>
+  <si>
+    <t>新喀里多尼亚</t>
+  </si>
+  <si>
+    <t>新西兰</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>智利</t>
+  </si>
+  <si>
+    <t>朝鲜</t>
+  </si>
+  <si>
+    <t>柬埔寨</t>
+  </si>
+  <si>
+    <t>格林纳达</t>
+  </si>
+  <si>
+    <t>格鲁吉亚</t>
+  </si>
+  <si>
+    <t>比利时</t>
+  </si>
+  <si>
+    <t>毛里塔尼亚</t>
+  </si>
+  <si>
+    <t>毛里求斯</t>
+  </si>
+  <si>
+    <t>汤加</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>法国</t>
+  </si>
+  <si>
+    <t>法属圣马丁</t>
+  </si>
+  <si>
+    <t>法属圭亚那</t>
+  </si>
+  <si>
+    <t>法属波利尼西亚</t>
+  </si>
+  <si>
+    <t>波兰</t>
+  </si>
+  <si>
+    <t>波多黎各</t>
+  </si>
+  <si>
+    <t>波斯尼亚和黑塞哥维那</t>
+  </si>
+  <si>
+    <t>泰国</t>
+  </si>
+  <si>
+    <t>津巴布韦</t>
+  </si>
+  <si>
+    <t>洪都拉斯</t>
+  </si>
+  <si>
+    <t>海地</t>
+  </si>
+  <si>
+    <t>澳大利亚</t>
+  </si>
+  <si>
+    <t>爱尔兰</t>
+  </si>
+  <si>
+    <t>爱沙尼亚</t>
+  </si>
+  <si>
+    <t>牙买加</t>
+  </si>
+  <si>
+    <t>特克斯和凯科斯群岛</t>
+  </si>
+  <si>
+    <t>特立尼达和多巴哥</t>
+  </si>
+  <si>
+    <t>玻利维亚</t>
+  </si>
+  <si>
+    <t>瑙鲁</t>
+  </si>
+  <si>
+    <t>瑞典</t>
+  </si>
+  <si>
+    <t>瑞士</t>
+  </si>
+  <si>
+    <t>瓜德罗普</t>
+  </si>
+  <si>
+    <t>瓦利斯和富图纳</t>
+  </si>
+  <si>
+    <t>瓦努阿图</t>
+  </si>
+  <si>
+    <t>留尼汪</t>
+  </si>
+  <si>
+    <t>白俄罗斯</t>
+  </si>
+  <si>
+    <t>百慕大</t>
+  </si>
+  <si>
+    <t>社会群岛</t>
+  </si>
+  <si>
+    <t>科威特</t>
+  </si>
+  <si>
+    <t>科摩罗</t>
+  </si>
+  <si>
+    <t>科特迪瓦</t>
+  </si>
+  <si>
+    <t>秘鲁</t>
+  </si>
+  <si>
+    <t>突尼斯</t>
+  </si>
+  <si>
+    <t>立陶宛</t>
+  </si>
+  <si>
+    <t>索马里</t>
+  </si>
+  <si>
+    <t>约旦</t>
+  </si>
+  <si>
+    <t>纳米比亚</t>
+  </si>
+  <si>
+    <t>缅甸</t>
+  </si>
+  <si>
+    <t>罗马尼亚</t>
+  </si>
+  <si>
+    <t>美国</t>
+  </si>
+  <si>
+    <t>美属维尔京群岛</t>
+  </si>
+  <si>
+    <t>美属萨摩亚</t>
+  </si>
+  <si>
+    <t>老挝</t>
+  </si>
+  <si>
+    <t>肯尼亚</t>
+  </si>
+  <si>
+    <t>芬兰</t>
+  </si>
+  <si>
+    <t>苏丹</t>
+  </si>
+  <si>
+    <t>苏里南</t>
+  </si>
+  <si>
+    <t>英国</t>
+  </si>
+  <si>
+    <t>英属印度洋领地</t>
+  </si>
+  <si>
+    <t>英属维尔京群岛</t>
+  </si>
+  <si>
+    <t>荷兰</t>
+  </si>
+  <si>
+    <t>荷属圣马丁</t>
+  </si>
+  <si>
+    <t>莫桑比克</t>
+  </si>
+  <si>
+    <t>莱索托</t>
+  </si>
+  <si>
+    <t>菲律宾</t>
+  </si>
+  <si>
+    <t>萨尔瓦多</t>
+  </si>
+  <si>
+    <t>萨摩亚</t>
+  </si>
+  <si>
+    <t>葡萄牙</t>
+  </si>
+  <si>
+    <t>蒙古</t>
+  </si>
+  <si>
+    <t>蒙特塞拉特</t>
+  </si>
+  <si>
+    <t>西撒哈拉</t>
+  </si>
+  <si>
+    <t>西班牙</t>
+  </si>
+  <si>
+    <t>贝宁</t>
+  </si>
+  <si>
+    <t>赞比亚</t>
+  </si>
+  <si>
+    <t>赤道几内亚</t>
+  </si>
+  <si>
+    <t>越南</t>
+  </si>
+  <si>
+    <t>阿塞拜疆</t>
+  </si>
+  <si>
+    <t>阿富汗</t>
+  </si>
+  <si>
+    <t>阿尔及利亚</t>
+  </si>
+  <si>
+    <t>阿尔巴尼亚</t>
+  </si>
+  <si>
+    <t>阿曼</t>
+  </si>
+  <si>
+    <t>阿根廷</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>阿鲁巴</t>
+  </si>
+  <si>
+    <t>非洲其他国家(地区)</t>
+  </si>
+  <si>
+    <t>韩国</t>
+  </si>
+  <si>
+    <t>马尔代夫</t>
+  </si>
+  <si>
+    <t>马拉维</t>
+  </si>
+  <si>
+    <t>马提尼克</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>马约特</t>
+  </si>
+  <si>
+    <t>马绍尔群岛</t>
+  </si>
+  <si>
+    <t>马耳他</t>
+  </si>
+  <si>
+    <t>马达加斯加</t>
+  </si>
+  <si>
+    <t>马里</t>
+  </si>
+  <si>
+    <t>黎巴嫩</t>
+  </si>
+  <si>
+    <t>黑山</t>
+  </si>
+  <si>
     <t>子区域</t>
   </si>
   <si>
-    <t>阿富汗</t>
-  </si>
-  <si>
-    <t>巴林</t>
-  </si>
-  <si>
-    <t>孟加拉国</t>
+    <t>欧洲</t>
   </si>
   <si>
     <t>南亚</t>
   </si>
   <si>
+    <t>东南亚</t>
+  </si>
+  <si>
+    <t>东亚</t>
+  </si>
+  <si>
+    <t>非洲</t>
+  </si>
+  <si>
+    <t>中亚</t>
+  </si>
+  <si>
+    <t>南美</t>
+  </si>
+  <si>
     <t>中东</t>
+  </si>
+  <si>
+    <t>中美洲</t>
+  </si>
+  <si>
+    <t>大洋洲</t>
+  </si>
+  <si>
+    <t>北美</t>
+  </si>
+  <si>
+    <t>加勒比</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>拉美</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -70,14 +815,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -365,43 +1119,2547 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C230"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" t="s">
+        <v>48</v>
+      </c>
+      <c r="C48" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" t="s">
+        <v>76</v>
+      </c>
+      <c r="C76" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C85" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>87</v>
+      </c>
+      <c r="C87" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" t="s">
+        <v>90</v>
+      </c>
+      <c r="C90" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>91</v>
+      </c>
+      <c r="C91" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" t="s">
+        <v>92</v>
+      </c>
+      <c r="C92" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>93</v>
+      </c>
+      <c r="C93" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" t="s">
+        <v>94</v>
+      </c>
+      <c r="C94" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" t="s">
+        <v>95</v>
+      </c>
+      <c r="C95" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" t="s">
+        <v>96</v>
+      </c>
+      <c r="C96" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>97</v>
+      </c>
+      <c r="C97" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>98</v>
+      </c>
+      <c r="C98" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>100</v>
+      </c>
+      <c r="C100" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>102</v>
+      </c>
+      <c r="C102" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>103</v>
+      </c>
+      <c r="C103" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>105</v>
+      </c>
+      <c r="C105" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" t="s">
+        <v>106</v>
+      </c>
+      <c r="C106" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" t="s">
+        <v>108</v>
+      </c>
+      <c r="C108" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109" t="s">
+        <v>109</v>
+      </c>
+      <c r="C109" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" t="s">
+        <v>110</v>
+      </c>
+      <c r="C110" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" t="s">
+        <v>111</v>
+      </c>
+      <c r="C111" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C113" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" t="s">
+        <v>114</v>
+      </c>
+      <c r="C114" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" t="s">
+        <v>115</v>
+      </c>
+      <c r="C115" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" t="s">
+        <v>116</v>
+      </c>
+      <c r="C116" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" t="s">
+        <v>117</v>
+      </c>
+      <c r="C117" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" t="s">
+        <v>118</v>
+      </c>
+      <c r="C118" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" t="s">
+        <v>119</v>
+      </c>
+      <c r="C119" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" t="s">
+        <v>120</v>
+      </c>
+      <c r="C120" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" t="s">
+        <v>121</v>
+      </c>
+      <c r="C121" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" t="s">
+        <v>122</v>
+      </c>
+      <c r="C122" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123" t="s">
+        <v>123</v>
+      </c>
+      <c r="C123" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" t="s">
+        <v>124</v>
+      </c>
+      <c r="C124" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" t="s">
+        <v>125</v>
+      </c>
+      <c r="C125" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" t="s">
+        <v>126</v>
+      </c>
+      <c r="C126" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" t="s">
+        <v>127</v>
+      </c>
+      <c r="C127" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" t="s">
+        <v>128</v>
+      </c>
+      <c r="C128" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" t="s">
+        <v>129</v>
+      </c>
+      <c r="C129" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" t="s">
+        <v>130</v>
+      </c>
+      <c r="C130" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" t="s">
+        <v>131</v>
+      </c>
+      <c r="C131" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" t="s">
+        <v>132</v>
+      </c>
+      <c r="C132" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" t="s">
+        <v>133</v>
+      </c>
+      <c r="C133" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" t="s">
+        <v>134</v>
+      </c>
+      <c r="C134" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" t="s">
+        <v>135</v>
+      </c>
+      <c r="C135" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" t="s">
+        <v>136</v>
+      </c>
+      <c r="C136" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" t="s">
+        <v>137</v>
+      </c>
+      <c r="C137" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+      <c r="B138" t="s">
+        <v>138</v>
+      </c>
+      <c r="C138" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+      <c r="B139" t="s">
+        <v>139</v>
+      </c>
+      <c r="C139" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+      <c r="B140" t="s">
+        <v>140</v>
+      </c>
+      <c r="C140" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+      <c r="B141" t="s">
+        <v>141</v>
+      </c>
+      <c r="C141" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+      <c r="B142" t="s">
+        <v>142</v>
+      </c>
+      <c r="C142" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+      <c r="B143" t="s">
+        <v>143</v>
+      </c>
+      <c r="C143" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+      <c r="B144" t="s">
+        <v>144</v>
+      </c>
+      <c r="C144" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+      <c r="B145" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+      <c r="B146" t="s">
+        <v>146</v>
+      </c>
+      <c r="C146" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+      <c r="B147" t="s">
+        <v>147</v>
+      </c>
+      <c r="C147" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+      <c r="B148" t="s">
+        <v>148</v>
+      </c>
+      <c r="C148" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" t="s">
+        <v>149</v>
+      </c>
+      <c r="C149" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+      <c r="B150" t="s">
+        <v>150</v>
+      </c>
+      <c r="C150" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+      <c r="B151" t="s">
+        <v>151</v>
+      </c>
+      <c r="C151" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+      <c r="B152" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" t="s">
+        <v>153</v>
+      </c>
+      <c r="C153" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" t="s">
+        <v>154</v>
+      </c>
+      <c r="C154" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>155</v>
+      </c>
+      <c r="C155" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" t="s">
+        <v>156</v>
+      </c>
+      <c r="C156" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" t="s">
+        <v>157</v>
+      </c>
+      <c r="C157" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" t="s">
+        <v>158</v>
+      </c>
+      <c r="C158" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+      <c r="B159" t="s">
+        <v>159</v>
+      </c>
+      <c r="C159" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+      <c r="B160" t="s">
+        <v>160</v>
+      </c>
+      <c r="C160" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" t="s">
+        <v>161</v>
+      </c>
+      <c r="C161" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162" t="s">
+        <v>162</v>
+      </c>
+      <c r="C162" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+      <c r="B163" t="s">
+        <v>163</v>
+      </c>
+      <c r="C163" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" t="s">
+        <v>164</v>
+      </c>
+      <c r="C164" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" t="s">
+        <v>165</v>
+      </c>
+      <c r="C165" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+      <c r="B166" t="s">
+        <v>166</v>
+      </c>
+      <c r="C166" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+      <c r="B167" t="s">
+        <v>167</v>
+      </c>
+      <c r="C167" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+      <c r="B168" t="s">
+        <v>168</v>
+      </c>
+      <c r="C168" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169" t="s">
+        <v>169</v>
+      </c>
+      <c r="C169" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+      <c r="B170" t="s">
+        <v>170</v>
+      </c>
+      <c r="C170" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+      <c r="B171" t="s">
+        <v>171</v>
+      </c>
+      <c r="C171" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+      <c r="B172" t="s">
+        <v>172</v>
+      </c>
+      <c r="C172" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+      <c r="B173" t="s">
+        <v>173</v>
+      </c>
+      <c r="C173" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+      <c r="B174" t="s">
+        <v>174</v>
+      </c>
+      <c r="C174" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+      <c r="B175" t="s">
+        <v>175</v>
+      </c>
+      <c r="C175" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+      <c r="B176" t="s">
+        <v>176</v>
+      </c>
+      <c r="C176" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+      <c r="B177" t="s">
+        <v>177</v>
+      </c>
+      <c r="C177" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" t="s">
+        <v>178</v>
+      </c>
+      <c r="C178" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+      <c r="B179" t="s">
+        <v>179</v>
+      </c>
+      <c r="C179" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" t="s">
+        <v>180</v>
+      </c>
+      <c r="C180" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>181</v>
+      </c>
+      <c r="C181" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>182</v>
+      </c>
+      <c r="C182" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+      <c r="B183" t="s">
+        <v>183</v>
+      </c>
+      <c r="C183" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+      <c r="B184" t="s">
+        <v>184</v>
+      </c>
+      <c r="C184" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+      <c r="B185" t="s">
+        <v>185</v>
+      </c>
+      <c r="C185" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+      <c r="B186" t="s">
+        <v>186</v>
+      </c>
+      <c r="C186" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+      <c r="B187" t="s">
+        <v>187</v>
+      </c>
+      <c r="C187" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+      <c r="B188" t="s">
+        <v>188</v>
+      </c>
+      <c r="C188" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+      <c r="B189" t="s">
+        <v>189</v>
+      </c>
+      <c r="C189" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+      <c r="B190" t="s">
+        <v>190</v>
+      </c>
+      <c r="C190" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+      <c r="B191" t="s">
+        <v>191</v>
+      </c>
+      <c r="C191" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+      <c r="B192" t="s">
+        <v>192</v>
+      </c>
+      <c r="C192" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+      <c r="B193" t="s">
+        <v>193</v>
+      </c>
+      <c r="C193" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+      <c r="B194" t="s">
+        <v>194</v>
+      </c>
+      <c r="C194" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+      <c r="B195" t="s">
+        <v>195</v>
+      </c>
+      <c r="C195" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+      <c r="B196" t="s">
+        <v>196</v>
+      </c>
+      <c r="C196" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+      <c r="B197" t="s">
+        <v>197</v>
+      </c>
+      <c r="C197" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+      <c r="B198" t="s">
+        <v>198</v>
+      </c>
+      <c r="C198" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s">
+        <v>199</v>
+      </c>
+      <c r="C199" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B200" t="s">
+        <v>200</v>
+      </c>
+      <c r="C200" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B201" t="s">
+        <v>201</v>
+      </c>
+      <c r="C201" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+      <c r="B202" t="s">
+        <v>202</v>
+      </c>
+      <c r="C202" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+      <c r="B203" t="s">
+        <v>203</v>
+      </c>
+      <c r="C203" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+      <c r="B204" t="s">
+        <v>204</v>
+      </c>
+      <c r="C204" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+      <c r="B205" t="s">
+        <v>205</v>
+      </c>
+      <c r="C205" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+      <c r="B206" t="s">
+        <v>206</v>
+      </c>
+      <c r="C206" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>207</v>
+      </c>
+      <c r="C207" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+      <c r="B208" t="s">
+        <v>208</v>
+      </c>
+      <c r="C208" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+      <c r="B209" t="s">
+        <v>209</v>
+      </c>
+      <c r="C209" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+      <c r="B210" t="s">
+        <v>210</v>
+      </c>
+      <c r="C210" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B211" t="s">
+        <v>211</v>
+      </c>
+      <c r="C211" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+      <c r="B212" t="s">
+        <v>212</v>
+      </c>
+      <c r="C212" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+      <c r="B213" t="s">
+        <v>213</v>
+      </c>
+      <c r="C213" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B214" t="s">
+        <v>214</v>
+      </c>
+      <c r="C214" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+      <c r="B215" t="s">
+        <v>215</v>
+      </c>
+      <c r="C215" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+      <c r="B216" t="s">
+        <v>216</v>
+      </c>
+      <c r="C216" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+      <c r="B217" t="s">
+        <v>217</v>
+      </c>
+      <c r="C217" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+      <c r="B218" t="s">
+        <v>218</v>
+      </c>
+      <c r="C218" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+      <c r="B219" t="s">
+        <v>219</v>
+      </c>
+      <c r="C219" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+      <c r="B220" t="s">
+        <v>220</v>
+      </c>
+      <c r="C220" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+      <c r="B221" t="s">
+        <v>221</v>
+      </c>
+      <c r="C221" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+      <c r="B222" t="s">
+        <v>222</v>
+      </c>
+      <c r="C222" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+      <c r="B223" t="s">
+        <v>223</v>
+      </c>
+      <c r="C223" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+      <c r="B224" t="s">
+        <v>224</v>
+      </c>
+      <c r="C224" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+      <c r="B225" t="s">
+        <v>225</v>
+      </c>
+      <c r="C225" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+      <c r="B226" t="s">
+        <v>226</v>
+      </c>
+      <c r="C226" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+      <c r="B227" t="s">
+        <v>227</v>
+      </c>
+      <c r="C227" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+      <c r="B228" t="s">
+        <v>228</v>
+      </c>
+      <c r="C228" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+      <c r="B229" t="s">
+        <v>229</v>
+      </c>
+      <c r="C229" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+      <c r="B230" t="s">
+        <v>230</v>
+      </c>
+      <c r="C230" t="s">
+        <v>232</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>